--- a/worklog/v2.2.3/s10/v4/metrics/outputs/review-20260923/10所指标规划_20260923.xlsx
+++ b/worklog/v2.2.3/s10/v4/metrics/outputs/review-20260923/10所指标规划_20260923.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'编制说明'!$A$1:$C$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'指标清单'!$A$1:$X$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'指标清单'!$A$1:$W$74</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'展现视图清单'!$A$1:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'落地前置条件'!$A$1:$F$9</definedName>
   </definedNames>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -540,7 +540,7 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="72" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>实施阶段</t>
@@ -548,248 +548,235 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>一期候选 20 条 / 二期候选 43 条 / 条件启用 10 条。条件启用指须先满足适用性前提（如会计制度、可比范围）才可启用。</t>
+          <t>一期 20 条：来源系统已具备、口径可当期确认，且多数是其他指标的上游，先做。
+二期 28 条：需补口径或补采集，在一期口径稳定后做。
+三期 15 条：依赖尚未建立的台账或尚未解决的系统前提（如设计更改台账、成果转化合同、产品成本核算、导出审批记录），前置问题解决后再排期。
+条件启用 10 条：适用性开关，不是排在最后。前提不成立（如会计制度不适用、无稳定批产产线）则一直不启用，与期次无关。</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>阶段为建议排序，不代表数据已就绪。</t>
+          <t>本列只按数据可得性排序，不代表业务重要性——业务重要性排序由院所确定。
+阶段为建议排序，不代表数据已就绪；一期范围最终以《落地前置条件》验源结果为准。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>实施优先级</t>
+          <t>指标类型</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>P1 20 条 / P2 35 条 / P3 18 条，按数据可得性划分，不按业务重要性划分。</t>
+          <t>原子 19 条、派生 52 条、复合 2 条。派生与复合指标均在“依赖指标编码”列写明上游。</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>P1=来源系统已具备且口径可确认；P2=需补口径或补采集；P3=依赖尚未解决的系统或制度前提。业务重要性排序由院所确定。</t>
+          <t>依赖关系决定建模顺序：上游指标未确认口径前，下游指标不得先行发布。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>指标类型</t>
+          <t>统一计算规则</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>原子 19 条、派生 52 条、复合 2 条。派生与复合指标均在“依赖指标编码”列写明上游。</t>
+          <t>金额统一币种、税口径与会计期间；流量跨期可加，期末存量不可加；百分比按分子分母重新汇总，不得对率取平均。</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>依赖关系决定建模顺序：上游指标未确认口径前，下游指标不得先行发布。</t>
+          <t>分母为 0 标“不适用”；缺字段标“不可计算”；只有确认范围内确无事件才填 0。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>统一计算规则</t>
+          <t>到期集合规则</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>金额统一币种、税口径与会计期间；流量跨期可加，期末存量不可加；百分比按分子分母重新汇总，不得对率取平均。</t>
+          <t>结题、里程碑、交付、整改类比率，分母为“本期应完成集合”，未完成且已到期的对象仍留在分母。</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>分母为 0 标“不适用”；缺字段标“不可计算”；只有确认范围内确无事件才填 0。</t>
+          <t>每个比率配套“期末逾期未完成数”绝对值指标，防止只看比率掩盖积压。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>到期集合规则</t>
+          <t>基线防漂移</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>结题、里程碑、交付、整改类比率，分母为“本期应完成集合”，未完成且已到期的对象仍留在分母。</t>
+          <t>原计划、批准调整计划、实际日期三者均留存；正式指标使用冻结的批准基线，并披露调整次数与影响。</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>每个比率配套“期末逾期未完成数”绝对值指标，防止只看比率掩盖积压。</t>
+          <t>禁止事后修改计划掩盖延期；计划取消须有批准记录与生效日期。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>基线防漂移</t>
+          <t>科研评价导向</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>原计划、批准调整计划、实际日期三者均留存；正式指标使用冻结的批准基线，并披露调整次数与影响。</t>
+          <t>专利与论文分开统计；以验收通过的代表性成果与任务履约观察贡献，不以论文数或人均数量排名。</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>禁止事后修改计划掩盖延期；计划取消须有批准记录与生效日期。</t>
+          <t>参照《国务院关于优化科研管理提升科研绩效若干措施的通知》（国发〔2018〕25号）代表性成果导向；非本单位考核制度认定。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>科研评价导向</t>
+          <t>经济性口径</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>专利与论文分开统计；以验收通过的代表性成果与任务履约观察贡献，不以论文数或人均数量排名。</t>
+          <t>科研经费结余不等于企业净利润；科研试验设备不宜直接套用固定资产投资回报率。</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>参照《国务院关于优化科研管理提升科研绩效若干措施的通知》（国发〔2018〕25号）代表性成果导向；非本单位考核制度认定。</t>
+          <t>涉及事业单位与企业两套制度差异的指标列为条件启用，由财务确认适用制度后启用。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>经济性口径</t>
+          <t>物料保障原则</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>科研经费结余不等于企业净利润；科研试验设备不宜直接套用固定资产投资回报率。</t>
+          <t>库存既要压降无效占用，也要保障专用备件与长周期物料。战略储备单列，未经评审不认定为呆滞。</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>涉及事业单位与企业两套制度差异的指标列为条件启用，由财务确认适用制度后启用。</t>
+          <t>批次、效期、质量冻结状态与项目可用范围共同决定可用量。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>物料保障原则</t>
+          <t>密级列的用法</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>库存既要压降无效占用，也要保障专用备件与长周期物料。战略储备单列，未经评审不认定为呆滞。</t>
+          <t>“建议数据密级”为讨论起点，供定密责任人使用。写作“内部（按项目下钻：秘密）”表示汇总可按内部管理、明细须按秘密管理。</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>批次、效期、质量冻结状态与项目可用范围共同决定可用量。</t>
+          <t>依据《国家秘密定密管理规定》（国家保密局令2025年第1号，2025-05-01 施行）的定密权限与知悉范围要求；本文件不代行定密。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>密级列的用法</t>
+          <t>密级不得反向推导</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>“建议数据密级”为讨论起点，供定密责任人使用。写作“内部（按项目下钻：秘密）”表示汇总可按内部管理、明细须按秘密管理。</t>
+          <t>汇总、脱敏、去标识不自动降密。由低密级数据关联聚合产生的结果，可能高于任一来源的密级。</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>依据《国家秘密定密管理规定》（国家保密局令2025年第1号，2025-05-01 施行）的定密权限与知悉范围要求；本文件不代行定密。</t>
+          <t>“聚合敏感度=高”的 20 条指标，其交叉筛选与批量导出须经保密部门单独审查。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>密级不得反向推导</t>
+          <t>人员密级与数据密级</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>汇总、脱敏、去标识不自动降密。由低密级数据关联聚合产生的结果，可能高于任一来源的密级。</t>
+          <t>两者是相互独立的标准，不得互相换算、不得混用名称。</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>“聚合敏感度=高”的 20 条指标，其交叉筛选与批量导出须经保密部门单独审查。</t>
+          <t>知悉范围按岗位职责与项目授权确定，不按人员密级自动放行。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>人员密级与数据密级</t>
+          <t>查看与导出控制</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>两者是相互独立的标准，不得互相换算、不得混用名称。</t>
+          <t>按人员角色、项目知悉范围及经批准的数据分类，分别控制查看、下钻、导出与共享。</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>知悉范围按岗位职责与项目授权确定，不按人员密级自动放行。</t>
+          <t>涉密与非涉密环境按本单位要求隔离；抑制规则、汇总层级与输出范围由保密部门批准，不设通用最小样本数。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>查看与导出控制</t>
+          <t>目标值与阈值</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>按人员角色、项目知悉范围及经批准的数据分类，分别控制查看、下钻、导出与共享。</t>
+          <t>本文件不预填行业通用目标、权重或红黄线。</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>涉密与非涉密环境按本单位要求隔离；抑制规则、汇总层级与输出范围由保密部门批准，不设通用最小样本数。</t>
+          <t>先取合同约定与上级制度门槛；无门槛的用本单位同类历史基线校准。目标值、预警阈值、目标依据三列留空待填。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>目标值与阈值</t>
+          <t>确认流程</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>本文件不预填行业通用目标、权重或红黄线。</t>
+          <t>①业务与数据责任人逐条确认适用性与字段；②保密部门审定密级与聚合敏感度；③财务确认会计制度适用项；④按《落地前置条件》完成数据验源后确定一期范围。</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>先取合同约定与上级制度门槛；无门槛的用本单位同类历史基线校准。目标值、预警阈值、目标依据三列留空待填。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>确认流程</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>①业务与数据责任人逐条确认适用性与字段；②保密部门审定密级与聚合敏感度；③财务确认会计制度适用项；④按《落地前置条件》完成数据验源后确定一期范围。</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>归口部门为职能角色建议，不是对现有组织架构的认定。</t>
         </is>
@@ -807,7 +794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X74"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -816,23 +803,23 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="42" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="26" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="26" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="18" customWidth="1" min="20" max="20"/>
-    <col width="54" customWidth="1" min="21" max="21"/>
-    <col width="32" customWidth="1" min="22" max="22"/>
-    <col width="20" customWidth="1" min="23" max="23"/>
+    <col width="18" customWidth="1" min="19" max="19"/>
+    <col width="54" customWidth="1" min="20" max="20"/>
+    <col width="32" customWidth="1" min="21" max="21"/>
+    <col width="20" customWidth="1" min="22" max="22"/>
+    <col width="28" customWidth="1" min="23" max="23"/>
     <col width="28" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
@@ -869,90 +856,85 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>实施优先级</t>
+          <t>驾驶舱</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>驾驶舱</t>
+          <t>单位</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>单位</t>
+          <t>定义与计算口径</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>定义与计算口径</t>
+          <t>统计粒度与时间口径</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>统计粒度与时间口径</t>
+          <t>更新频率</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>更新频率</t>
+          <t>数据来源及必需字段</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源及必需字段</t>
+          <t>归口部门</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>归口部门</t>
+          <t>建议数据密级（待定密责任人审定）</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>建议数据密级（待定密责任人审定）</t>
+          <t>建议知悉范围</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>建议知悉范围</t>
+          <t>聚合敏感度</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>聚合敏感度</t>
+          <t>目标值（待审定）</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>目标值（待审定）</t>
+          <t>预警阈值（待审定）</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>预警阈值（待审定）</t>
+          <t>目标依据（待填）</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>目标依据（待填）</t>
+          <t>口径说明与特殊规则</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>口径说明与特殊规则</t>
+          <t>查看与输出控制</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>查看与输出控制</t>
+          <t>确认状态</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>确认状态</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>责任人确认意见</t>
         </is>
@@ -982,83 +964,78 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>项</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>按正式立项批准日期落在统计期的项目ID去重计数</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>按正式立项批准日期落在统计期的项目ID去重计数</t>
+          <t>期间流量；项目类型、责任部门</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>期间流量；项目类型、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>项目系统：项目ID、批准日期、状态、父项目ID</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>项目系统：项目ID、批准日期、状态、父项目ID</t>
+          <t>科研计划部门</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>科研计划部门</t>
+          <t>内部（按项目下钻：秘密）</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>内部（按项目下钻：秘密）</t>
+          <t>科研计划、院所领导</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>科研计划、院所领导</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q2" s="2" t="inlineStr"/>
       <c r="R2" s="2" t="inlineStr"/>
       <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>系统新建时间不能替代批准立项时间；父子项目选择同一层级</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>系统新建时间不能替代批准立项时间；父子项目选择同一层级</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1092,83 +1069,78 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应结题且在批准期限内完成验收结题的项目数÷本期应结题项目数×100%</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>本期应结题且在批准期限内完成验收结题的项目数÷本期应结题项目数×100%</t>
+          <t>按基线到期日归期；项目类型、责任部门</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>按基线到期日归期；项目类型、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>项目系统：基线结题日、批准变更、验收结题日、项目ID</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>项目系统：基线结题日、批准变更、验收结题日、项目ID</t>
+          <t>科研计划部门</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>科研计划部门</t>
+          <t>内部（按项目下钻：秘密）</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>内部（按项目下钻：秘密）</t>
+          <t>科研计划、院所领导</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>科研计划、院所领导</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q3" s="2" t="inlineStr"/>
       <c r="R3" s="2" t="inlineStr"/>
       <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>替换结题数÷立项数；逾期未结题进入分母；冻结原始及批准调整基线</t>
+        </is>
+      </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>替换结题数÷立项数；逾期未结题进入分母；冻结原始及批准调整基线</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1198,83 +1170,78 @@
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应完成且在基线期限内验收通过的里程碑数÷本期应完成里程碑数×100%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>本期应完成且在基线期限内验收通过的里程碑数÷本期应完成里程碑数×100%</t>
+          <t>项目×里程碑；按到期日归期</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>项目×里程碑；按到期日归期</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>项目系统：节点ID、计划基线、验收完成日、变更记录</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>项目系统：节点ID、计划基线、验收完成日、变更记录</t>
+          <t>科研计划部门</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>科研计划部门</t>
+          <t>内部（按项目下钻：秘密）</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>内部（按项目下钻：秘密）</t>
+          <t>科研计划、项目负责人</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>科研计划、项目负责人</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q4" s="2" t="inlineStr"/>
       <c r="R4" s="2" t="inlineStr"/>
       <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>未完成到期节点不可遗漏；关键节点单列，不用普通节点稀释</t>
+        </is>
+      </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>未完成到期节点不可遗漏；关键节点单列，不用普通节点稀释</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1308,83 +1275,78 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>天</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>天</t>
+          <t>本期验收结题项目的Σ(结题日期－批准立项日期)÷本期验收结题项目数</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>本期验收结题项目的Σ(结题日期－批准立项日期)÷本期验收结题项目数</t>
+          <t>结题 cohort；同项目类型及复杂度比较</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>结题 cohort；同项目类型及复杂度比较</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>项目系统：批准立项日、结题日、项目类型</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>项目系统：批准立项日、结题日、项目类型</t>
+          <t>科研计划部门</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>科研计划部门</t>
+          <t>内部（按项目下钻：秘密）</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>内部（按项目下钻：秘密）</t>
+          <t>科研计划</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>科研计划</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q5" s="2" t="inlineStr"/>
       <c r="R5" s="2" t="inlineStr"/>
       <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>仅代表已结题项目；在研老项目另看超期数，不跨类型排名</t>
+        </is>
+      </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>仅代表已结题项目；在研老项目另看超期数，不跨类型排名</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1414,83 +1376,78 @@
       <c r="E6" s="2" t="inlineStr"/>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应归档项目中截至期末全部必备文档审核通过的项目数÷本期应归档项目数×100%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>本期应归档项目中截至期末全部必备文档审核通过的项目数÷本期应归档项目数×100%</t>
+          <t>项目×适用归档清单版本；按归档截止日归期</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>项目×适用归档清单版本；按归档截止日归期</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>档案系统：清单版本、应归档日、审核状态、项目ID</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>档案系统：清单版本、应归档日、审核状态、项目ID</t>
+          <t>档案管理部门</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>档案管理部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>科研计划、档案</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>科研计划、档案</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q6" s="2" t="inlineStr"/>
       <c r="R6" s="2" t="inlineStr"/>
       <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>合并重复文档齐备率；清单须包含适用交付资料；齐备不等于及时</t>
+        </is>
+      </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>合并重复文档齐备率；清单须包含适用交付资料；齐备不等于及时</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1520,83 +1477,78 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>期末有效批复预算按项目类别汇总，并展示各类金额÷总额×100%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>期末有效批复预算按项目类别汇总，并展示各类金额÷总额×100%</t>
+          <t>期末存量；预算版本、项目类别</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>期末存量；预算版本、项目类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>预算系统：有效预算版本、项目叶级预算、类别</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>预算系统：有效预算版本、项目叶级预算、类别</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>科研计划、财务、院所领导</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>科研计划、财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
       <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>原经费分布未说明预算/支出；本指标只表达预算，父子层级不可重复加总</t>
+        </is>
+      </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>原经费分布未说明预算/支出；本指标只表达预算，父子层级不可重复加总</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1626,83 +1578,78 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>件</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>按授权日期落在本期的专利唯一编号去重计数</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>按授权日期落在本期的专利唯一编号去重计数</t>
+          <t>期间流量；专利类别、责任部门</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>期间流量；专利类别、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>知识产权台账：授权号、授权日期、类别、权属</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>知识产权台账：授权号、授权日期、类别、权属</t>
+          <t>科研成果部门</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>科研成果部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>科技管理、知识产权</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>科技管理、知识产权</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
       <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>从专利/论文数拆出；不与申请数混算，不作为单独绩效排名</t>
+        </is>
+      </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>从专利/论文数拆出；不与申请数混算，不作为单独绩效排名</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1732,83 +1679,78 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>篇</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>篇</t>
+          <t>本期正式发表且完成适用公开审查的论文ID去重计数</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>本期正式发表且完成适用公开审查的论文ID去重计数</t>
+          <t>发表日期归期；部门、成果类型</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>发表日期归期；部门、成果类型</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>成果台账：论文ID、发表日、审查记录、重复标识</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>成果台账：论文ID、发表日、审查记录、重复标识</t>
+          <t>科研成果部门</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>科研成果部门</t>
+          <t>公开（发表前载体：按原密级）</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>公开（发表前载体：按原密级）</t>
+          <t>科技管理、保密</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>科技管理、保密</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q9" s="2" t="inlineStr"/>
       <c r="R9" s="2" t="inlineStr"/>
       <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>涉密成果不因不能公开而扣分；不得将内部报告当公开论文</t>
+        </is>
+      </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>涉密成果不因不能公开而扣分；不得将内部报告当公开论文</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1838,83 +1780,78 @@
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>本期生效合同金额＋本期生效增补金额－本期生效冲减金额</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>本期生效合同金额＋本期生效增补金额－本期生效冲减金额</t>
+          <t>合同及变更事件；不含重复主从合同</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>合同及变更事件；不含重复主从合同</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>合同系统：合同ID、生效日、变更金额、币种税口径</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>合同系统：合同ID、生效日、变更金额、币种税口径</t>
+          <t>成果转化部门</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>成果转化部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>科技管理、财务、院所领导</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>科技管理、财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q10" s="2" t="inlineStr"/>
       <c r="R10" s="2" t="inlineStr"/>
       <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>合同额不是收入或回款；不以公开交易规模评价全部科研成果</t>
+        </is>
+      </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>合同额不是收入或回款；不以公开交易规模评价全部科研成果</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -1944,83 +1881,78 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>项</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>截至期末已批准且状态为执行中的项目ID去重计数</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>截至期末已批准且状态为执行中的项目ID去重计数</t>
+          <t>期末快照；部门、项目类型</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>期末快照；部门、项目类型</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>项目系统：状态履历、生效时间、项目ID</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>项目系统：状态履历、生效时间、项目ID</t>
+          <t>科研计划部门</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>科研计划部门</t>
+          <t>内部（按项目下钻：秘密）</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>内部（按项目下钻：秘密）</t>
+          <t>科研计划、院所领导</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>科研计划、院所领导</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q11" s="2" t="inlineStr"/>
       <c r="R11" s="2" t="inlineStr"/>
       <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>暂停、撤销、结题分别列示；不能只用未结题状态判定</t>
+        </is>
+      </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>暂停、撤销、结题分别列示；不能只用未结题状态判定</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2050,83 +1982,78 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>项</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>截至期末基线结题日已过且尚未验收结题的项目ID去重计数</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>截至期末基线结题日已过且尚未验收结题的项目ID去重计数</t>
+          <t>期末快照；项目类型、责任部门</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>期末快照；项目类型、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>项目系统：基线日期、实际结题日、状态履历</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>项目系统：基线日期、实际结题日、状态履历</t>
+          <t>科研计划部门</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>科研计划部门</t>
+          <t>内部（按项目下钻：秘密）</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>内部（按项目下钻：秘密）</t>
+          <t>科研计划、院所领导</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>科研计划、院所领导</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q12" s="2" t="inlineStr"/>
       <c r="R12" s="2" t="inlineStr"/>
       <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>与当期延期结题分开；已批准取消项目按生效日留痕处理</t>
+        </is>
+      </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>与当期延期结题分开；已批准取消项目按生效日留痕处理</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2160,83 +2087,78 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>同一项目范围自立项至期末累计确认支出÷期末有效全周期批复预算×100%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>同一项目范围自立项至期末累计确认支出÷期末有效全周期批复预算×100%</t>
+          <t>项目全周期累计；经费性质、责任部门</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>项目全周期累计；经费性质、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务/预算：项目支出凭证、有效预算、截止日期</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>财务/预算：项目支出凭证、有效预算、截止日期</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>科研计划、财务、院所领导</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>科研计划、财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q13" s="2" t="inlineStr"/>
       <c r="R13" s="2" t="inlineStr"/>
       <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>先确定支出会计口径；不可把当月支出除全周期预算；并非越高越好</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>先确定支出会计口径；不可把当月支出除全周期预算；并非越高越好</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2266,83 +2188,78 @@
       <c r="E14" s="2" t="inlineStr"/>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应归档且全部必备文档在归档截止日前审核通过的项目数÷本期应归档项目数×100%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>本期应归档且全部必备文档在归档截止日前审核通过的项目数÷本期应归档项目数×100%</t>
+          <t>按归档到期日归期；项目类型</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>按归档到期日归期；项目类型</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>档案系统：应归档日、末份必备文档审核日、清单</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>档案系统：应归档日、末份必备文档审核日、清单</t>
+          <t>档案管理部门</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>档案管理部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>科研计划、档案</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>科研计划、档案</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q14" s="2" t="inlineStr"/>
       <c r="R14" s="2" t="inlineStr"/>
       <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>原分母总结题项目未考虑归档宽限期；与齐备率共用清单</t>
+        </is>
+      </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>原分母总结题项目未考虑归档宽限期；与齐备率共用清单</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2372,83 +2289,78 @@
       <c r="E15" s="2" t="inlineStr"/>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期到期且全部适用对象按期执行并验证的更改单数÷本期到期更改单数×100%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>本期到期且全部适用对象按期执行并验证的更改单数÷本期到期更改单数×100%</t>
+          <t>更改单×到期日；项目、责任部门</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>更改单×到期日；项目、责任部门</t>
+          <t>日采集/月汇总</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>日采集/月汇总</t>
+          <t>PLM：批准版本、影响对象、期限、实施验证</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>PLM：批准版本、影响对象、期限、实施验证</t>
+          <t>技术管理部门</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>技术管理部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>设计、质量、项目负责人</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>设计、质量、项目负责人</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q15" s="2" t="inlineStr"/>
       <c r="R15" s="2" t="inlineStr"/>
       <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>借鉴参考模型，分子分母统一更改单；不能把任务数除以订单数</t>
+        </is>
+      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>借鉴参考模型，分子分母统一更改单；不能把任务数除以订单数</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2478,83 +2390,78 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>项</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>按正式结题批准日期落在统计期的项目ID去重计数</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>按正式结题批准日期落在统计期的项目ID去重计数</t>
+          <t>期间流量；项目类型、责任部门</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>期间流量；项目类型、责任部门</t>
+          <t>月</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>项目系统：项目ID、结题批准日期、结题状态、父项目ID</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>项目系统：项目ID、结题批准日期、结题状态、父项目ID</t>
+          <t>科研计划部门</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>科研计划部门</t>
+          <t>内部（按项目下钻：秘密）</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>内部（按项目下钻：秘密）</t>
+          <t>科研计划、院所领导</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>科研计划、院所领导</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q16" s="2" t="inlineStr"/>
       <c r="R16" s="2" t="inlineStr"/>
       <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>与 PRJ02 共用同一结题批准口径，两处不得各算一套；本指标同时是 PRJ02 到期按期结题率的分子来源。结题批准日期以正式批准为准，系统状态变更时间不作数。</t>
+        </is>
+      </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>与 PRJ02 共用同一结题批准口径，两处不得各算一套；本指标同时是 PRJ02 到期按期结题率的分子来源。结题批准日期以正式批准为准，系统状态变更时间不作数。</t>
+          <t>按项目知悉范围/部门授权</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2584,83 +2491,78 @@
       <c r="E17" s="2" t="inlineStr"/>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>汇总本期财务已关账收入科目的净发生额</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>汇总本期财务已关账收入科目的净发生额</t>
+          <t>法人核算主体×会计期间；收入类别</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>法人核算主体×会计期间；收入类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务：科目映射、凭证、冲销、核算主体</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>财务：科目映射、凭证、冲销、核算主体</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>财务、院所领导</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q17" s="2" t="inlineStr"/>
       <c r="R17" s="2" t="inlineStr"/>
       <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>限定适用会计制度；不把拨款到账、合同额直接当收入</t>
+        </is>
+      </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>限定适用会计制度；不把拨款到账、合同额直接当收入</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2690,83 +2592,78 @@
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>汇总本期与FIN01同制度的已关账费用成本净发生额</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>汇总本期与FIN01同制度的已关账费用成本净发生额</t>
+          <t>法人核算主体×会计期间；费用类别</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>法人核算主体×会计期间；费用类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务：科目映射、成本费用凭证、结转</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>财务：科目映射、成本费用凭证、结转</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>财务、院所领导</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q18" s="2" t="inlineStr"/>
       <c r="R18" s="2" t="inlineStr"/>
       <c r="S18" s="2" t="inlineStr"/>
-      <c r="T18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>原总支出易混合现金支付与费用；本口径不含购置资产现金全额</t>
+        </is>
+      </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>原总支出易混合现金支付与费用；本口径不含购置资产现金全额</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X18" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2800,83 +2697,78 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>FIN01当期确认收入－FIN02当期费用及成本</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>FIN01当期确认收入－FIN02当期费用及成本</t>
+          <t>与FIN01、FIN02完全同范围同期间</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>与FIN01、FIN02完全同范围同期间</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务：FIN01、FIN02及科目映射</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>财务：FIN01、FIN02及科目映射</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>财务、院所领导</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q19" s="2" t="inlineStr"/>
       <c r="R19" s="2" t="inlineStr"/>
       <c r="S19" s="2" t="inlineStr"/>
-      <c r="T19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>不直接称净利润或法定净结余；法定报表指标按适用制度另行映射</t>
+        </is>
+      </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>不直接称净利润或法定净结余；法定报表指标按适用制度另行映射</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X19" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -2910,83 +2802,78 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>元/件</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>元/件</t>
+          <t>本期结转到同规格合格完工产品的制造成本÷该批合格完工数量</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>本期结转到同规格合格完工产品的制造成本÷该批合格完工数量</t>
+          <t>产品规格×成本结算期；计量单位一致</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>产品规格×成本结算期；计量单位一致</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>成本/MES：成本对象、完工转入成本、合格数量</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>成本/MES：成本对象、完工转入成本、合格数量</t>
+          <t>财务及生产部门</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>财务及生产部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>财务、生产、院所领导</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>财务、生产、院所领导</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q20" s="2" t="inlineStr"/>
       <c r="R20" s="2" t="inlineStr"/>
       <c r="S20" s="2" t="inlineStr"/>
-      <c r="T20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>合并单位产出成本与单位制造成本；科研项目不得以项目数充当产量</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>合并单位产出成本与单位制造成本；科研项目不得以项目数充当产量</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X20" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3016,83 +2903,78 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>实际执行有效科研试验任务小时÷批准可供科研使用小时×100%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>实际执行有效科研试验任务小时÷批准可供科研使用小时×100%</t>
+          <t>设备×月；设备类别、责任部门</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>设备×月；设备类别、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>设备预约/运行：任务小时、批准开放时段、校准维护</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>设备预约/运行：任务小时、批准开放时段、校准维护</t>
+          <t>设备管理部门</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>设备管理部门</t>
+          <t>内部（按设备下钻：秘密）</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>内部（按设备下钻：秘密）</t>
+          <t>设备、科研计划</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>设备、科研计划</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q21" s="2" t="inlineStr"/>
       <c r="R21" s="2" t="inlineStr"/>
       <c r="S21" s="2" t="inlineStr"/>
-      <c r="T21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>替代固定资产ROI；战略备用设备单列，不因低利用率简单淘汰</t>
+        </is>
+      </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>替代固定资产ROI；战略备用设备单列，不因低利用率简单淘汰</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X21" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3127,78 +3009,73 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>(累计实际三公经费－同期间累计批准预算)÷同期间累计批准预算×100%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>(累计实际三公经费－同期间累计批准预算)÷同期间累计批准预算×100%</t>
+          <t>年初累计；适用经费分类</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>年初累计；适用经费分类</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务/预算：三公分类、支出、预算版本</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>财务/预算：三公分类、支出、预算版本</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>财务、纪检</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>财务、纪检</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q22" s="2" t="inlineStr"/>
       <c r="R22" s="2" t="inlineStr"/>
       <c r="S22" s="2" t="inlineStr"/>
-      <c r="T22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>适用范围须财务确认；零预算发生支出另报金额异常，不算百分比</t>
+        </is>
+      </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>适用范围须财务确认；零预算发生支出另报金额异常，不算百分比</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X22" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3233,78 +3110,73 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>指数</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>指数</t>
+          <t>Σ(本期同质物料价格×基期固定数量)÷Σ(基期价格×基期固定数量)×100</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Σ(本期同质物料价格×基期固定数量)÷Σ(基期价格×基期固定数量)×100</t>
+          <t>固定样本篮子；同规格、质量等级、税币口径</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>固定样本篮子；同规格、质量等级、税币口径</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>采购：规格、质量等级、基期量价、本期可比价</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>采购：规格、质量等级、基期量价、本期可比价</t>
+          <t>采购部门</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>采购部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>采购、财务</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>采购、财务</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q23" s="2" t="inlineStr"/>
       <c r="R23" s="2" t="inlineStr"/>
       <c r="S23" s="2" t="inlineStr"/>
-      <c r="T23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>基期为100；缺少可比样本不硬算；定制研制件不与通用件直接比价</t>
+        </is>
+      </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>基期为100；缺少可比样本不硬算；定制研制件不与通用件直接比价</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X23" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3334,83 +3206,78 @@
       <c r="E24" s="2" t="inlineStr"/>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>同一期末总负债÷总资产×100%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>同一期末总负债÷总资产×100%</t>
+          <t>法人主体×期末；财务报表口径</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>法人主体×期末；财务报表口径</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务：期末资产总额、负债总额</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>财务：期末资产总额、负债总额</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>财务、院所领导</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q24" s="2" t="inlineStr"/>
       <c r="R24" s="2" t="inlineStr"/>
       <c r="S24" s="2" t="inlineStr"/>
-      <c r="T24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>不拆到无独立资产负债表的部门；不预设统一红线</t>
+        </is>
+      </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>不拆到无独立资产负债表的部门；不预设统一红线</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X24" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3445,78 +3312,73 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>同期间已确认净利润÷营业收入×100%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>同期间已确认净利润÷营业收入×100%</t>
+          <t>法人主体×会计期间</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>法人主体×会计期间</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务：净利润、营业收入、制度口径</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>财务：净利润、营业收入、制度口径</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>财务、院所领导</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q25" s="2" t="inlineStr"/>
       <c r="R25" s="2" t="inlineStr"/>
       <c r="S25" s="2" t="inlineStr"/>
-      <c r="T25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>不与科研事业单位收支结余混用；非经营科研任务不按利润率排序</t>
+        </is>
+      </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>不与科研事业单位收支结余混用；非经营科研任务不按利润率排序</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X25" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3551,78 +3413,73 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>同期间销售费用、管理费用及财务费用之和÷营业收入×100%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>同期间销售费用、管理费用及财务费用之和÷营业收入×100%</t>
+          <t>法人主体×会计期间</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>法人主体×会计期间</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务：费用科目映射、营业收入</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>财务：费用科目映射、营业收入</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>财务、院所领导</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>财务、院所领导</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q26" s="2" t="inlineStr"/>
       <c r="R26" s="2" t="inlineStr"/>
       <c r="S26" s="2" t="inlineStr"/>
-      <c r="T26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>明确是否含研发费用，当前建议不含且单列；映射待财务审定</t>
+        </is>
+      </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>明确是否含研发费用，当前建议不含且单列；映射待财务审定</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X26" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3656,83 +3513,78 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>截至期末各次已批准预算调整金额绝对值之和÷原始批复预算×100%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>截至期末各次已批准预算调整金额绝对值之和÷原始批复预算×100%</t>
+          <t>项目全周期累计；预算版本</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>项目全周期累计；预算版本</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>预算：原始预算、每次调整金额及批准记录</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>预算：原始预算、每次调整金额及批准记录</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>财务、科研计划</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>财务、科研计划</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q27" s="2" t="inlineStr"/>
       <c r="R27" s="2" t="inlineStr"/>
       <c r="S27" s="2" t="inlineStr"/>
-      <c r="T27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>与净增减区分，防止往返调整抵消；调整不自动视为不合理</t>
+        </is>
+      </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>与净增减区分，防止往返调整抵消；调整不自动视为不合理</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X27" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3766,83 +3618,78 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期经审核认定合规的支出笔数 ÷ 本期已审核支出笔数 × 100%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>本期经审核认定合规的支出笔数 ÷ 本期已审核支出笔数 × 100%</t>
+          <t>期间流量；责任部门、支出类别</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>期间流量；责任部门、支出类别</t>
+          <t>月</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>月</t>
+          <t>财务系统：凭证号、支出笔数、审核结论、审核日期；审计/纪检：不合规认定记录</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>财务系统：凭证号、支出笔数、审核结论、审核日期；审计/纪检：不合规认定记录</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>财务、审计、纪检</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>财务、审计、纪检</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q28" s="2" t="inlineStr"/>
       <c r="R28" s="2" t="inlineStr"/>
       <c r="S28" s="2" t="inlineStr"/>
-      <c r="T28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>分母为“已完成审核”的支出笔数，未审核笔数不得计入分母充数。按笔数而非金额统计，避免大额合规支出稀释小额违规。合规认定标准由财务与审计共同确认，不由报表侧自拟。</t>
+        </is>
+      </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>分母为“已完成审核”的支出笔数，未审核笔数不得计入分母充数。按笔数而非金额统计，避免大额合规支出稀释小额违规。合规认定标准由财务与审计共同确认，不由报表侧自拟。</t>
+          <t>按部门授权；不合规明细仅对财务、审计、纪检开放</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>按部门授权；不合规明细仅对财务、审计、纪检开放</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X28" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3881,78 +3728,73 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>万元/人</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>万元/人</t>
+          <t>期末在研项目批复预算合计 ÷ 期末科研岗在册人数</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>期末在研项目批复预算合计 ÷ 期末科研岗在册人数</t>
+          <t>期末存量；责任部门、项目类型</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>期末存量；责任部门、项目类型</t>
+          <t>季度</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>季度</t>
+          <t>项目系统：在研项目、批复预算；HR系统：科研岗在册人数、岗位类别</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>项目系统：在研项目、批复预算；HR系统：科研岗在册人数、岗位类别</t>
+          <t>科研计划部门</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>科研计划部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>科研计划、人力、院所领导</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>科研计划、人力、院所领导</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q29" s="2" t="inlineStr"/>
       <c r="R29" s="2" t="inlineStr"/>
       <c r="S29" s="2" t="inlineStr"/>
-      <c r="T29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>仅作资源配置描述，不用于部门或个人排名：预研、型号、技改项目的经费强度天然差异大，跨类型比较无意义。启用前须确认科研岗口径（是否含试制、外协）与项目类型分组。</t>
+        </is>
+      </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>仅作资源配置描述，不用于部门或个人排名：预研、型号、技改项目的经费强度天然差异大，跨类型比较无意义。启用前须确认科研岗口径（是否含试制、外协）与项目类型分组。</t>
+          <t>部门级可见；按项目下钻按知悉范围授权</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>部门级可见；按项目下钻按知悉范围授权</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X29" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -3982,83 +3824,78 @@
       <c r="E30" s="2" t="inlineStr"/>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期到期交期行中在约定日前足量到货的行数÷本期到期交期行数×100%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>本期到期交期行中在约定日前足量到货的行数÷本期到期交期行数×100%</t>
+          <t>采购订单×行×交期；供应商、物料类别</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>采购订单×行×交期；供应商、物料类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP：订单行、分批交期、约定数量、收货日期数量</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>ERP：订单行、分批交期、约定数量、收货日期数量</t>
+          <t>采购部门</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>采购部门</t>
+          <t>内部（按供应商/物料下钻：秘密）</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>内部（按供应商/物料下钻：秘密）</t>
+          <t>采购、科研计划</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>采购、科研计划</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q30" s="2" t="inlineStr"/>
       <c r="R30" s="2" t="inlineStr"/>
       <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>逾期未到货计分母；分批交期独立；验收合格另看QUA02</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>逾期未到货计分母；分批交期独立；验收合格另看QUA02</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X30" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4088,83 +3925,78 @@
       <c r="E31" s="2" t="inlineStr"/>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>天</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>天</t>
+          <t>本期收齐采购行的Σ(足量到货日－订单生效日)÷本期收齐行数</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>本期收齐采购行的Σ(足量到货日－订单生效日)÷本期收齐行数</t>
+          <t>收齐日归期；采购行、物料类别</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>收齐日归期；采购行、物料类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP：订单生效日、分批收货、足量到货日</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>ERP：订单生效日、分批收货、足量到货日</t>
+          <t>采购部门</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>采购部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>采购</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>采购</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q31" s="2" t="inlineStr"/>
       <c r="R31" s="2" t="inlineStr"/>
       <c r="S31" s="2" t="inlineStr"/>
-      <c r="T31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>只反映已收齐 cohort；未到货积压另看SUP11，避免快单偏差</t>
+        </is>
+      </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>只反映已收齐 cohort；未到货积压另看SUP11，避免快单偏差</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X31" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4199,78 +4031,73 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>(同质采购加权均价－已批准参考价)÷已批准参考价×100%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>(同质采购加权均价－已批准参考价)÷已批准参考价×100%</t>
+          <t>物料规格×质量等级×期间</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>物料规格×质量等级×期间</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>采购：金额、数量、质量等级、参考价版本</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>采购：金额、数量、质量等级、参考价版本</t>
+          <t>采购部门</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>采购部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>采购、审计</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>采购、审计</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q32" s="2" t="inlineStr"/>
       <c r="R32" s="2" t="inlineStr"/>
       <c r="S32" s="2" t="inlineStr"/>
-      <c r="T32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>不以降价抵消质量/保密要求；币种税口径一致；无参考价不计算</t>
+        </is>
+      </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>不以降价抵消质量/保密要求；币种税口径一致；无参考价不计算</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X32" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4309,78 +4136,73 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>分项展示</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>分项展示</t>
+          <t>分别展示SUP01到货率、QUA02质量率及资格状态；暂不合成为总分</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>分别展示SUP01到货率、QUA02质量率及资格状态；暂不合成为总分</t>
+          <t>供应商×评价期；资质有效期</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>供应商×评价期；资质有效期</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>供应商台账、采购与质检：分项结果、资格证明</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>供应商台账、采购与质检：分项结果、资格证明</t>
+          <t>采购及质量部门</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>采购及质量部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>采购、质量</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>采购、质量</t>
-        </is>
-      </c>
-      <c r="Q33" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q33" s="2" t="inlineStr"/>
       <c r="R33" s="2" t="inlineStr"/>
       <c r="S33" s="2" t="inlineStr"/>
-      <c r="T33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>替代未定义权重的综合分；资质/保密条件不允许被低价或高交付分抵消</t>
+        </is>
+      </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>替代未定义权重的综合分；资质/保密条件不允许被低价或高交付分抵消</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X33" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4410,83 +4232,78 @@
       <c r="E34" s="2" t="inlineStr"/>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期到期需求行中未按时足量提供合格可用物料的行数÷本期到期有效需求行数×100%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>本期到期需求行中未按时足量提供合格可用物料的行数÷本期到期有效需求行数×100%</t>
+          <t>需求行×需求日期；项目、物料类别</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>需求行×需求日期；项目、物料类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>需求/库存：需求量、需用日、合格可用分配量</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>需求/库存：需求量、需用日、合格可用分配量</t>
+          <t>物资及计划部门</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>物资及计划部门</t>
+          <t>内部（按物料下钻：秘密）</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>内部（按物料下钻：秘密）</t>
+          <t>采购、科研计划、生产</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>采购、科研计划、生产</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q34" s="2" t="inlineStr"/>
       <c r="R34" s="2" t="inlineStr"/>
       <c r="S34" s="2" t="inlineStr"/>
-      <c r="T34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>替换跨物料数量相加；冻结、隔离、不属于该项目可用范围的库存不可算满足</t>
+        </is>
+      </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>替换跨物料数量相加；冻结、隔离、不属于该项目可用范围的库存不可算满足</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X34" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4516,83 +4333,78 @@
       <c r="E35" s="2" t="inlineStr"/>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应下单且在要求日期前完成有效订单的需求行数÷本期应下单需求行数×100%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>本期应下单且在要求日期前完成有效订单的需求行数÷本期应下单需求行数×100%</t>
+          <t>需求行×要求下单日；采购类别</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>需求行×要求下单日；采购类别</t>
+          <t>日采集/月汇总</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>日采集/月汇总</t>
+          <t>采购：批准需求、要求下单日、订单生效日、关联关系</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>采购：批准需求、要求下单日、订单生效日、关联关系</t>
+          <t>采购部门</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>采购部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>采购</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>采购</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q35" s="2" t="inlineStr"/>
       <c r="R35" s="2" t="inlineStr"/>
       <c r="S35" s="2" t="inlineStr"/>
-      <c r="T35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>与到货率不同；要求日期由批准需用日和采购提前期推导，不回填美化</t>
+        </is>
+      </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>与到货率不同；要求日期由批准需用日和采购提前期推导，不回填美化</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X35" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4622,83 +4434,78 @@
       <c r="E36" s="2" t="inlineStr"/>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>同物料类别本期采购净额前N家供应商之和÷该类别采购净额×100%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>同物料类别本期采购净额前N家供应商之和÷该类别采购净额×100%</t>
+          <t>物料类别×期间；N待批准</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>物料类别×期间；N待批准</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP：供应商统一ID、采购净额、物料类别</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>ERP：供应商统一ID、采购净额、物料类别</t>
+          <t>采购部门</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>采购部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>采购、保密、院所领导</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>采购、保密、院所领导</t>
-        </is>
-      </c>
-      <c r="Q36" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr"/>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>N和集团关联供应商合并规则固定；集中不自动等于高风险</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>N和集团关联供应商合并规则固定；集中不自动等于高风险</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X36" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4728,83 +4535,78 @@
       <c r="E37" s="2" t="inlineStr"/>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>冻结关键物料清单中仅一家具备有效供货资格的物料种类数÷关键物料种类数×100%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>冻结关键物料清单中仅一家具备有效供货资格的物料种类数÷关键物料种类数×100%</t>
+          <t>关键物料清单×期末；类别</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>关键物料清单×期末；类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>供应商/物料：关键清单、合格来源、资格有效期</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>供应商/物料：关键清单、合格来源、资格有效期</t>
+          <t>采购及技术部门</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>采购及技术部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>采购、保密、院所领导</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>采购、保密、院所领导</t>
-        </is>
-      </c>
-      <c r="Q37" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q37" s="2" t="inlineStr"/>
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>替代不透明供应风险指数；设计指定单一来源单列原因，不强行替代</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>替代不透明供应风险指数；设计指定单一来源单列原因，不强行替代</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X37" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4834,83 +4636,78 @@
       <c r="E38" s="2" t="inlineStr"/>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期到期且交付、质量、必需资料等适用义务均按期满足的合同数÷本期到期合同数×100%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>本期到期且交付、质量、必需资料等适用义务均按期满足的合同数÷本期到期合同数×100%</t>
+          <t>合同×履约截止期；供应商</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>合同×履约截止期；供应商</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>合同：义务清单、到期日、验收、文件、关闭依据</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>合同：义务清单、到期日、验收、文件、关闭依据</t>
+          <t>采购及合同部门</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>采购及合同部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>采购、法务</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>采购、法务</t>
-        </is>
-      </c>
-      <c r="Q38" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="inlineStr"/>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>不能把交货当全部履约；无明确到期或义务清单时先不计算</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>不能把交货当全部履约；无明确到期或义务清单时先不计算</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X38" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -4940,83 +4737,78 @@
       <c r="E39" s="2" t="inlineStr"/>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期按批准紧急程序生效的采购净额÷本期采购净额×100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>本期按批准紧急程序生效的采购净额÷本期采购净额×100%</t>
+          <t>订单生效期；项目、采购类别</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>订单生效期；项目、采购类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>采购：紧急标识、批准记录、净额</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>采购：紧急标识、批准记录、净额</t>
+          <t>采购部门</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>采购部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>采购、审计、纪检</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>采购、审计、纪检</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q39" s="2" t="inlineStr"/>
       <c r="R39" s="2" t="inlineStr"/>
       <c r="S39" s="2" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>紧急采购不是未经流程采购；违规绕流程另报异常件数</t>
+        </is>
+      </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>紧急采购不是未经流程采购；违规绕流程另报异常件数</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X39" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5046,83 +4838,78 @@
       <c r="E40" s="2" t="inlineStr"/>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>行</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>行</t>
+          <t>期末约定到货日已过但累计收货量仍不足的交期行去重数</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>期末约定到货日已过但累计收货量仍不足的交期行去重数</t>
+          <t>期末快照；供应商、物料类别</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>期末快照；供应商、物料类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP：交期行、约定日数量、累计收货</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>ERP：交期行、约定日数量、累计收货</t>
+          <t>采购部门</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>采购部门</t>
+          <t>内部（按物料下钻：秘密）</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>内部（按物料下钻：秘密）</t>
+          <t>采购、科研计划</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>采购、科研计划</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q40" s="2" t="inlineStr"/>
       <c r="R40" s="2" t="inlineStr"/>
       <c r="S40" s="2" t="inlineStr"/>
-      <c r="T40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>补齐采购周期幸存者偏差；同时展示正向逾期天数，不用提前到货抵消</t>
+        </is>
+      </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>补齐采购周期幸存者偏差；同时展示正向逾期天数，不用提前到货抵消</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5152,83 +4939,78 @@
       <c r="E41" s="2" t="inlineStr"/>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>Σ达到分类闲置期限且已评审列为待处置的库存账面金额</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Σ达到分类闲置期限且已评审列为待处置的库存账面金额</t>
+          <t>库存批次×期末；物料类别、项目占用</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>库存批次×期末；物料类别、项目占用</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP/WMS：余额、末次有效领用日、闲置阈值、评审状态</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>ERP/WMS：余额、末次有效领用日、闲置阈值、评审状态</t>
+          <t>物资管理部门</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>物资管理部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>仓储、财务</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>仓储、财务</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q41" s="2" t="inlineStr"/>
       <c r="R41" s="2" t="inlineStr"/>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>先区分战略储备、专用备件及冻结物料；超期未动用不自动等于可处置</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>先区分战略储备、专用备件及冻结物料；超期未动用不自动等于可处置</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X41" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5262,83 +5044,78 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>次/期</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>次/期</t>
+          <t>本期生产科研净领用材料成本÷同期原材料日均账面余额</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>本期生产科研净领用材料成本÷同期原材料日均账面余额</t>
+          <t>原材料账；期间、物料类别</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>原材料账；期间、物料类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP/财务：净领用成本、每日库存金额、退料</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>ERP/财务：净领用成本、每日库存金额、退料</t>
+          <t>物资及财务部门</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>物资及财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>仓储、财务</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>仓储、财务</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr"/>
       <c r="S42" s="2" t="inlineStr"/>
-      <c r="T42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>明确替代通用库存周转率；不能把销货成本和材料领用任选；储备单列</t>
+        </is>
+      </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>明确替代通用库存周转率；不能把销货成本和材料领用任选；储备单列</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X42" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5368,83 +5145,78 @@
       <c r="E43" s="2" t="inlineStr"/>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>万元</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>万元</t>
+          <t>Σ期末在账库存数量×对应账面单位成本，与财务存货账核对</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Σ期末在账库存数量×对应账面单位成本，与财务存货账核对</t>
+          <t>物料×批次×仓库×期末</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>物料×批次×仓库×期末</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP/WMS/财务：库存快照、计价、所有权、对账</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>ERP/WMS/财务：库存快照、计价、所有权、对账</t>
+          <t>物资及财务部门</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>物资及财务部门</t>
+          <t>内部（按物料明细：秘密）</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>内部（按物料明细：秘密）</t>
+          <t>仓储、财务</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>仓储、财务</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr"/>
       <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>参考问题清单反映余额来源待确认；不能仅以不完整入出库单推算</t>
+        </is>
+      </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>参考问题清单反映余额来源待确认；不能仅以不完整入出库单推算</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X43" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5478,83 +5250,78 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>某互斥闲置时长区间的期末库存金额÷期末库存总金额×100%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>某互斥闲置时长区间的期末库存金额÷期末库存总金额×100%</t>
+          <t>期末；0至3、超过3至6、超过6至12、超过12月</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>期末；0至3、超过3至6、超过6至12、超过12月</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP：末次有效领用日、余额、储备标识</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>ERP：末次有效领用日、余额、储备标识</t>
+          <t>物资管理部门</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>物资管理部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>仓储、财务</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>仓储、财务</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr"/>
       <c r="S44" s="2" t="inlineStr"/>
-      <c r="T44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>按领用间隔分类而非入库龄；内部移库不重置；储备与待处置分开展示</t>
+        </is>
+      </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>按领用间隔分类而非入库龄；内部移库不重置；储备与待处置分开展示</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X44" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5588,83 +5355,78 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>有效期在期末后批准预警窗口内的库存金额÷有有效期管理的库存总金额×100%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>有效期在期末后批准预警窗口内的库存金额÷有有效期管理的库存总金额×100%</t>
+          <t>批次×期末；窗口按物料类别批准</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>批次×期末；窗口按物料类别批准</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>WMS：失效日、批次、余额、预警天数</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>WMS：失效日、批次、余额、预警天数</t>
+          <t>物资及质量部门</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>物资及质量部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>仓储、质量</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>仓储、质量</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr"/>
       <c r="S45" s="2" t="inlineStr"/>
-      <c r="T45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>已过期单列；无效期数据列缺失，不算安全；不用SKU数掩盖金额风险</t>
+        </is>
+      </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>已过期单列；无效期数据列缺失，不算安全；不用SKU数掩盖金额风险</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X45" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5698,83 +5460,78 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>Σ绝对值(实盘数量－冻结账面数量)×账面单位成本÷被盘点范围账面金额×100%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Σ绝对值(实盘数量－冻结账面数量)×账面单位成本÷被盘点范围账面金额×100%</t>
+          <t>盘点批次；统一截止时点与计价</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>盘点批次；统一截止时点与计价</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>WMS：冻结账、实盘量、单位成本、复核记录</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>WMS：冻结账、实盘量、单位成本、复核记录</t>
+          <t>物资及财务部门</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>物资及财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>仓储、财务、审计</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>仓储、财务、审计</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr"/>
       <c r="S46" s="2" t="inlineStr"/>
-      <c r="T46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>修正盈亏互相抵消；账面零但实物存在另报盘盈金额；仅代表已盘范围</t>
+        </is>
+      </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>修正盈亏互相抵消；账面零但实物存在另报盘盈金额；仅代表已盘范围</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X46" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5804,83 +5561,78 @@
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期到期且按基线日足量合格完工的订单数÷本期到期订单数×100%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>本期到期且按基线日足量合格完工的订单数÷本期到期订单数×100%</t>
+          <t>生产订单×到期日；产品类别</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>生产订单×到期日；产品类别</t>
+          <t>日采集/月汇总</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>日采集/月汇总</t>
+          <t>MES/ERP：基线、合格完工量、要求量、完成日</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>MES/ERP：基线、合格完工量、要求量、完成日</t>
+          <t>生产管理部门</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>生产管理部门</t>
+          <t>内部（按产品下钻：秘密）</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>内部（按产品下钻：秘密）</t>
+          <t>生产、计划</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>生产、计划</t>
-        </is>
-      </c>
-      <c r="Q47" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr"/>
       <c r="S47" s="2" t="inlineStr"/>
-      <c r="T47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>逾期未完成订单进入分母；按试制/批产区分；不等同客户验收交付</t>
+        </is>
+      </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>逾期未完成订单进入分母；按试制/批产区分；不等同客户验收交付</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X47" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -5919,78 +5671,73 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>运行时间÷计划生产时间×理想单件时间×总产量÷运行时间×合格产量÷总产量×100%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>运行时间÷计划生产时间×理想单件时间×总产量÷运行时间×合格产量÷总产量×100%</t>
+          <t>设备×同工艺产品×班次</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>设备×同工艺产品×班次</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>MES：计划时间、运行时间、理想节拍、产量、合格量</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>MES：计划时间、运行时间、理想节拍、产量、合格量</t>
+          <t>生产及设备部门</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>生产及设备部门</t>
+          <t>内部（按产品下钻：秘密）</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>内部（按产品下钻：秘密）</t>
+          <t>生产、设备</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>生产、设备</t>
-        </is>
-      </c>
-      <c r="Q48" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="2" t="inlineStr"/>
       <c r="S48" s="2" t="inlineStr"/>
-      <c r="T48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>仅适用节拍可靠的批产；研发试验设备用FIN05；异质工序不可简单均值</t>
+        </is>
+      </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>仅适用节拍可靠的批产；研发试验设备用FIN05；异质工序不可简单均值</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X48" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6020,83 +5767,78 @@
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>天</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>天</t>
+          <t>本期合格完工批次Σ(完工日－实际投料日)÷本期合格完工批次数</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>本期合格完工批次Σ(完工日－实际投料日)÷本期合格完工批次数</t>
+          <t>生产批×完工期；产品族、试制/批产</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>生产批×完工期；产品族、试制/批产</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>MES：投料日、合格完工日、批次ID</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>MES：投料日、合格完工日、批次ID</t>
+          <t>生产管理部门</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>生产管理部门</t>
+          <t>内部（按产品下钻：秘密）</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>内部（按产品下钻：秘密）</t>
+          <t>生产、计划</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>生产、计划</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q49" s="2" t="inlineStr"/>
       <c r="R49" s="2" t="inlineStr"/>
       <c r="S49" s="2" t="inlineStr"/>
-      <c r="T49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>整批完工口径需固定；同步关注在制超期，不只观察已完成批次</t>
+        </is>
+      </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>整批完工口径需固定；同步关注在制超期，不只观察已完成批次</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X49" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6126,83 +5868,78 @@
       <c r="E50" s="2" t="inlineStr"/>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>件</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>件</t>
+          <t>期末已投料尚未合格完工的在制品数量，按同规格同单位分别汇总</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>期末已投料尚未合格完工的在制品数量，按同规格同单位分别汇总</t>
+          <t>期末快照；产品规格、工序</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>期末快照；产品规格、工序</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>MES/盘点：在制状态、数量、计量单位、工序</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>MES/盘点：在制状态、数量、计量单位、工序</t>
+          <t>生产管理部门</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>生产管理部门</t>
+          <t>内部（按产品下钻：秘密）</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>内部（按产品下钻：秘密）</t>
+          <t>生产、仓储</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>生产、仓储</t>
-        </is>
-      </c>
-      <c r="Q50" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr"/>
       <c r="S50" s="2" t="inlineStr"/>
-      <c r="T50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>不能跨不同单位或规格加总为一个全所产量；报废与待处置单列</t>
+        </is>
+      </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>不能跨不同单位或规格加总为一个全所产量；报废与待处置单列</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X50" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6232,83 +5969,78 @@
       <c r="E51" s="2" t="inlineStr"/>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>计划运行时段内故障停机小时÷计划运行小时×100%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>计划运行时段内故障停机小时÷计划运行小时×100%</t>
+          <t>设备×月；设备类别</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>设备×月；设备类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>设备：故障起止、计划运行时段、停机分类</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>设备：故障起止、计划运行时段、停机分类</t>
+          <t>设备管理部门</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>设备管理部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>设备、生产</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>设备、生产</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr"/>
       <c r="S51" s="2" t="inlineStr"/>
-      <c r="T51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>替代故障次数÷设备数的模糊故障率；跨期停机按时段切分，重叠去重</t>
+        </is>
+      </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>替代故障次数÷设备数的模糊故障率；跨期停机按时段切分，重叠去重</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X51" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6343,78 +6075,73 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>千瓦时/件</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>千瓦时/件</t>
+          <t>同产品边界可归集用电量÷同期合格完工数量</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>同产品边界可归集用电量÷同期合格完工数量</t>
+          <t>产品族×期间；能耗边界固定</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>产品族×期间；能耗边界固定</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>能源/MES：分表电量、分摊规则、合格产量</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>能源/MES：分表电量、分摊规则、合格产量</t>
+          <t>能源及生产部门</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>能源及生产部门</t>
+          <t>内部（按产品下钻：秘密）</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>内部（按产品下钻：秘密）</t>
+          <t>生产、能源</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>生产、能源</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q52" s="2" t="inlineStr"/>
       <c r="R52" s="2" t="inlineStr"/>
       <c r="S52" s="2" t="inlineStr"/>
-      <c r="T52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>本版仅用电；蒸汽燃气需另立单位或审批折标系数；试验不套用件产量</t>
+        </is>
+      </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>本版仅用电；蒸汽燃气需另立单位或审批折标系数；试验不套用件产量</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X52" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6444,83 +6171,78 @@
       <c r="E53" s="2" t="inlineStr"/>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期首次检验完成且一次判定合格批次数÷本期首次检验完成批次数×100%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>本期首次检验完成且一次判定合格批次数÷本期首次检验完成批次数×100%</t>
+          <t>固定检验环节×检验批；完成期</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>固定检验环节×检验批；完成期</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>质检：批次ID、首检标识、结论、返工复检标识</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>质检：批次ID、首检标识、结论、返工复检标识</t>
+          <t>质量部门</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>质量部门</t>
+          <t>内部（按产品下钻：秘密）</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>内部（按产品下钻：秘密）</t>
+          <t>质量、生产</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>质量、生产</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q53" s="2" t="inlineStr"/>
       <c r="R53" s="2" t="inlineStr"/>
       <c r="S53" s="2" t="inlineStr"/>
-      <c r="T53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr">
+        <is>
+          <t>原数量/批次混用；本版采用批次，不混入复检结果；未检批次另列</t>
+        </is>
+      </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>原数量/批次混用；本版采用批次，不混入复检结果；未检批次另列</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X53" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6550,83 +6272,78 @@
       <c r="E54" s="2" t="inlineStr"/>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期完成首次检验并判定合格的来料批次÷本期完成首次检验的来料批次×100%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>本期完成首次检验并判定合格的来料批次÷本期完成首次检验的来料批次×100%</t>
+          <t>供应商×物料批次×检验完成期</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>供应商×物料批次×检验完成期</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>质检/ERP：来料批号、首次检验结论、完成日</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>质检/ERP：来料批号、首次检验结论、完成日</t>
+          <t>质量部门</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>质量部门</t>
+          <t>内部（按供应商下钻：秘密）</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>内部（按供应商下钻：秘密）</t>
+          <t>质量、采购</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>质量、采购</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q54" s="2" t="inlineStr"/>
       <c r="R54" s="2" t="inlineStr"/>
       <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>原分母到货批次混入未检；让步接收、复检合格单列，不算首次合格</t>
+        </is>
+      </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>原分母到货批次混入未检；让步接收、复检合格单列，不算首次合格</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X54" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6656,83 +6373,78 @@
       <c r="E55" s="2" t="inlineStr"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期到期且在要求日前经有效性验证关闭的问题数÷本期到期应关闭问题数×100%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>本期到期且在要求日前经有效性验证关闭的问题数÷本期到期应关闭问题数×100%</t>
+          <t>问题ID×到期日；等级、责任部门</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>问题ID×到期日；等级、责任部门</t>
+          <t>日采集/月汇总</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>日采集/月汇总</t>
+          <t>质量台账：问题ID、责任、期限、验证、关闭日</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>质量台账：问题ID、责任、期限、验证、关闭日</t>
+          <t>质量部门</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>质量部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>质量、相关责任部门</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>质量、相关责任部门</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q55" s="2" t="inlineStr"/>
       <c r="R55" s="2" t="inlineStr"/>
       <c r="S55" s="2" t="inlineStr"/>
-      <c r="T55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr">
+        <is>
+          <t>参考不合格票及时关闭率；不能用处理意见填写代替有效性验证</t>
+        </is>
+      </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>参考不合格票及时关闭率；不能用处理意见填写代替有效性验证</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X55" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6762,83 +6474,78 @@
       <c r="E56" s="2" t="inlineStr"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>是</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>项</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>批准重大问题范围内，期末超过处理期限且未验证关闭的问题ID去重数</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>批准重大问题范围内，期末超过处理期限且未验证关闭的问题ID去重数</t>
+          <t>期末快照；项目类型、责任部门</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>期末快照；项目类型、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>质量台账：批准等级、截止日、验证状态</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>质量台账：批准等级、截止日、验证状态</t>
+          <t>质量部门</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>质量部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>质量、院所领导</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>质量、院所领导</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q56" s="2" t="inlineStr"/>
       <c r="R56" s="2" t="inlineStr"/>
       <c r="S56" s="2" t="inlineStr"/>
-      <c r="T56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr">
+        <is>
+          <t>重大等级按单位批准标准；不以普通问题高关闭率抵消重大问题</t>
+        </is>
+      </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>重大等级按单位批准标准；不以普通问题高关闭率抵消重大问题</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X56" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6868,83 +6575,78 @@
       <c r="E57" s="2" t="inlineStr"/>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期交付中适用追溯链及必需资料审核齐备的批次数÷本期交付批次数×100%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>本期交付中适用追溯链及必需资料审核齐备的批次数÷本期交付批次数×100%</t>
+          <t>交付批次；产品类别</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>交付批次；产品类别</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>质量/档案：批号、物料来源、检验、版本、资料审核</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>质量/档案：批号、物料来源、检验、版本、资料审核</t>
+          <t>质量及档案部门</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>质量及档案部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>质量、档案、交付</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>质量、档案、交付</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q57" s="2" t="inlineStr"/>
       <c r="R57" s="2" t="inlineStr"/>
       <c r="S57" s="2" t="inlineStr"/>
-      <c r="T57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>只记录链路齐备和审核结果；详细技术参数保持原授权域内</t>
+        </is>
+      </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>只记录链路齐备和审核结果；详细技术参数保持原授权域内</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X57" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -6974,83 +6676,78 @@
       <c r="E58" s="2" t="inlineStr"/>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>专岗</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>专岗</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期到期且按期经授权人员复核关闭的整改项数÷本期到期应整改项数×100%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>本期到期且按期经授权人员复核关闭的整改项数÷本期到期应整改项数×100%</t>
+          <t>整改项×到期日；责任单位</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>整改项×到期日；责任单位</t>
+          <t>日采集/月汇总</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>日采集/月汇总</t>
+          <t>受控保密台账：编号、期限、复核结论、关闭日</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>受控保密台账：编号、期限、复核结论、关闭日</t>
+          <t>保密管理部门</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>保密管理部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>保密专岗、院所领导</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>保密专岗、院所领导</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q58" s="2" t="inlineStr"/>
       <c r="R58" s="2" t="inlineStr"/>
       <c r="S58" s="2" t="inlineStr"/>
-      <c r="T58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>汇总仅限授权域；不在普通驾驶舱展示问题细节与涉密对象</t>
+        </is>
+      </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>汇总仅限授权域；不在普通驾驶舱展示问题细节与涉密对象</t>
+          <t>仅保密/授权管理岗位；审批后汇总，明细留受控域</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>仅保密/授权管理岗位；审批后汇总，明细留受控域</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X58" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7080,83 +6777,78 @@
       <c r="E59" s="2" t="inlineStr"/>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>专岗</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>专岗</t>
+          <t>项</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>期末超过批准期限且未完成复核关闭的整改项去重数</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>期末超过批准期限且未完成复核关闭的整改项去重数</t>
+          <t>期末快照；授权责任范围</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>期末快照；授权责任范围</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>受控保密台账：编号、期限、状态</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>受控保密台账：编号、期限、状态</t>
+          <t>保密管理部门</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>保密管理部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>保密专岗、院所领导</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>保密专岗、院所领导</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q59" s="2" t="inlineStr"/>
       <c r="R59" s="2" t="inlineStr"/>
       <c r="S59" s="2" t="inlineStr"/>
-      <c r="T59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>与整改及时率配套；低问题发现数或零记录不等于保密工作良好</t>
+        </is>
+      </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>与整改及时率配套；低问题发现数或零记录不等于保密工作良好</t>
+          <t>仅保密/授权管理岗位；审批后汇总，明细留受控域</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>仅保密/授权管理岗位；审批后汇总，明细留受控域</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X59" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7186,83 +6878,78 @@
       <c r="E60" s="2" t="inlineStr"/>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>专岗</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>专岗</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应复核且按期完成权限及必要性复核的授权记录数÷本期应复核授权记录数×100%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>本期应复核且按期完成权限及必要性复核的授权记录数÷本期应复核授权记录数×100%</t>
+          <t>用户×资源×授权周期；授权域</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>用户×资源×授权周期；授权域</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>权限台账：授权ID、期限、复核结果、撤销记录</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>权限台账：授权ID、期限、复核结果、撤销记录</t>
+          <t>保密及信息化部门</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>保密及信息化部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>保密专岗、信息化</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>保密专岗、信息化</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q60" s="2" t="inlineStr"/>
       <c r="R60" s="2" t="inlineStr"/>
       <c r="S60" s="2" t="inlineStr"/>
-      <c r="T60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>角色权限和项目知悉范围同时检查；离岗变更撤权另查逾期例外</t>
+        </is>
+      </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>角色权限和项目知悉范围同时检查；离岗变更撤权另查逾期例外</t>
+          <t>仅保密/授权管理岗位；审批后汇总，明细留受控域</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>仅保密/授权管理岗位；审批后汇总，明细留受控域</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X60" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7292,83 +6979,78 @@
       <c r="E61" s="2" t="inlineStr"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>专岗</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>专岗</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期受检导出中审批对象、范围、接收方及用途均匹配的记录数÷本期受检导出记录数×100%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>本期受检导出中审批对象、范围、接收方及用途均匹配的记录数÷本期受检导出记录数×100%</t>
+          <t>导出事件；检查范围和抽样量披露</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>导出事件；检查范围和抽样量披露</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>审批/审计：导出ID、审批ID、对象范围、接收方</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>审批/审计：导出ID、审批ID、对象范围、接收方</t>
+          <t>保密及信息化部门</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>保密及信息化部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>保密专岗、信息化</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>保密专岗、信息化</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q61" s="2" t="inlineStr"/>
       <c r="R61" s="2" t="inlineStr"/>
       <c r="S61" s="2" t="inlineStr"/>
-      <c r="T61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>抽检结论不推断全量；无审批/审计日志列不可评价，不报100%</t>
+        </is>
+      </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>抽检结论不推断全量；无审批/审计日志列不可评价，不报100%</t>
+          <t>仅保密/授权管理岗位；审批后汇总，明细留受控域</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>仅保密/授权管理岗位；审批后汇总，明细留受控域</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X61" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7398,83 +7080,78 @@
       <c r="E62" s="2" t="inlineStr"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期到期且按期经复核消除的安全隐患数÷本期到期应整改隐患数×100%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>本期到期且按期经复核消除的安全隐患数÷本期到期应整改隐患数×100%</t>
+          <t>隐患ID×到期日；责任区域</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>隐患ID×到期日；责任区域</t>
+          <t>日采集/月汇总</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>日采集/月汇总</t>
+          <t>安全台账：等级、期限、整改、复核日</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>安全台账：等级、期限、整改、复核日</t>
+          <t>安全管理部门</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>安全管理部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>安全、保密专岗</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>安全、保密专岗</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q62" s="2" t="inlineStr"/>
       <c r="R62" s="2" t="inlineStr"/>
       <c r="S62" s="2" t="inlineStr"/>
-      <c r="T62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr">
+        <is>
+          <t>重大隐患另列，不以加权平均抵消；参考模型分母应改为到期集合</t>
+        </is>
+      </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>重大隐患另列，不以加权平均抵消；参考模型分母应改为到期集合</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X62" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7504,83 +7181,78 @@
       <c r="E63" s="2" t="inlineStr"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应刷新且按期完成取数、校验与责任确认的指标实例数÷本期应刷新指标实例数×100%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>本期应刷新且按期完成取数、校验与责任确认的指标实例数÷本期应刷新指标实例数×100%</t>
+          <t>指标编码×授权范围×统计期</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>指标编码×授权范围×统计期</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>指标台账：刷新截止、取数状态、校验、确认</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>指标台账：刷新截止、取数状态、校验、确认</t>
+          <t>信息化及业务归口</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>信息化及业务归口</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>数据管理、信息化</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>数据管理、信息化</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q63" s="2" t="inlineStr"/>
       <c r="R63" s="2" t="inlineStr"/>
       <c r="S63" s="2" t="inlineStr"/>
-      <c r="T63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>系统成功不等于业务数据就绪；缺数、未关账、超时分别标记</t>
+        </is>
+      </c>
       <c r="U63" s="2" t="inlineStr">
         <is>
-          <t>系统成功不等于业务数据就绪；缺数、未关账、超时分别标记</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7614,83 +7286,78 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>项</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>期末ERP库存、仓储记录及财务存货对账仍未解释关闭的差异ID去重数</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>期末ERP库存、仓储记录及财务存货对账仍未解释关闭的差异ID去重数</t>
+          <t>差异ID×期末；仓库、差异类型</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>差异ID×期末；仓库、差异类型</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>ERP/WMS/财务：对账范围、差异、责任、关闭记录</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>ERP/WMS/财务：对账范围、差异、责任、关闭记录</t>
+          <t>物资及财务部门</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>物资及财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>数据管理、仓储、财务</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>数据管理、仓储、财务</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q64" s="2" t="inlineStr"/>
       <c r="R64" s="2" t="inlineStr"/>
       <c r="S64" s="2" t="inlineStr"/>
-      <c r="T64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>先明确对账覆盖范围；无对账不能填零，需显示尚未对账</t>
+        </is>
+      </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>先明确对账覆盖范围；无对账不能填零，需显示尚未对账</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X64" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7720,83 +7387,78 @@
       <c r="E65" s="2" t="inlineStr"/>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>期末某主岗位类别在岗人数÷期末在岗总人数×100%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>期末某主岗位类别在岗人数÷期末在岗总人数×100%</t>
+          <t>期末快照；主岗位类别、部门</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>期末快照；主岗位类别、部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>HR：人员ID、主岗位、在岗状态、组织履历</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>HR：人员ID、主岗位、在岗状态、组织履历</t>
+          <t>人力资源部门</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>人力资源部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>人力、院所领导</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>人力、院所领导</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q65" s="2" t="inlineStr"/>
       <c r="R65" s="2" t="inlineStr"/>
       <c r="S65" s="2" t="inlineStr"/>
-      <c r="T65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>科研/技术/管理分类应互斥穷尽；兼职只按确定主岗位统计</t>
+        </is>
+      </c>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>科研/技术/管理分类应互斥穷尽；兼职只按确定主岗位统计</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X65" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7826,83 +7488,78 @@
       <c r="E66" s="2" t="inlineStr"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>期间主动离职核心人才人数÷期间核心人才月均在岗人数×100%</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>期间主动离职核心人才人数÷期间核心人才月均在岗人数×100%</t>
+          <t>滚动12月为主；核心人才名录版本</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>滚动12月为主；核心人才名录版本</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>HR：核心名录、离职原因、月均人数</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>HR：核心名录、离职原因、月均人数</t>
+          <t>人力资源部门</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>人力资源部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>人力、保密、院所领导</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>人力、保密、院所领导</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q66" s="2" t="inlineStr"/>
       <c r="R66" s="2" t="inlineStr"/>
       <c r="S66" s="2" t="inlineStr"/>
-      <c r="T66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr">
+        <is>
+          <t>核心名录先冻结；退休、内部调动与主动离职分开；小样本限制展示</t>
+        </is>
+      </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>核心名录先冻结；退休、内部调动与主动离职分开；小样本限制展示</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X66" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -7932,83 +7589,78 @@
       <c r="E67" s="2" t="inlineStr"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>人岗天</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>人岗天</t>
+          <t>Σ期间每日关键岗位批准编制数与实际合格在岗数的正差</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Σ期间每日关键岗位批准编制数与实际合格在岗数的正差</t>
+          <t>批准岗位×日；部门、岗位类别</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>批准岗位×日；部门、岗位类别</t>
+          <t>日采集/月汇总</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>日采集/月汇总</t>
+          <t>HR：编制生效日、空缺日、任职日、资格</t>
         </is>
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>HR：编制生效日、空缺日、任职日、资格</t>
+          <t>人力资源部门</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>人力资源部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>人力、保密、院所领导</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>人力、保密、院所领导</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q67" s="2" t="inlineStr"/>
       <c r="R67" s="2" t="inlineStr"/>
       <c r="S67" s="2" t="inlineStr"/>
-      <c r="T67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>按缺口人数累计；同岗多名缺员不可只算一次；月末未补齐继续累计</t>
+        </is>
+      </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>按缺口人数累计；同岗多名缺员不可只算一次；月末未补齐继续累计</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X67" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -8038,83 +7690,78 @@
       <c r="E68" s="2" t="inlineStr"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>元/人</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>元/人</t>
+          <t>同期间应付职工薪酬÷期间月均在岗人数</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>同期间应付职工薪酬÷期间月均在岗人数</t>
+          <t>月；同用工范围、责任部门</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>月；同用工范围、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>HR/财务：应付薪酬范围、月均人数</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>HR/财务：应付薪酬范围、月均人数</t>
+          <t>人力资源及财务</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>人力资源及财务</t>
+          <t>内部（按部门下钻：秘密）</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>内部（按部门下钻：秘密）</t>
+          <t>人力、财务</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>人力、财务</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q68" s="2" t="inlineStr"/>
       <c r="R68" s="2" t="inlineStr"/>
       <c r="S68" s="2" t="inlineStr"/>
-      <c r="T68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr">
+        <is>
+          <t>不混用发放与计提；仅授权汇总，禁止通过小部门反推个人收入</t>
+        </is>
+      </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>不混用发放与计提；仅授权汇总，禁止通过小部门反推个人收入</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -8144,83 +7791,78 @@
       <c r="E69" s="2" t="inlineStr"/>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>项</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>项</t>
+          <t>本期通过规定验收的代表性成果ID按类型分别去重计数</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>本期通过规定验收的代表性成果ID按类型分别去重计数</t>
+          <t>成果类型×验收期；关联项目、责任部门</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>成果类型×验收期；关联项目、责任部门</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>成果台账：成果ID、类型、验收结论、贡献归属</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>成果台账：成果ID、类型、验收结论、贡献归属</t>
+          <t>科研成果部门</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>科研成果部门</t>
+          <t>秘密</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>秘密</t>
+          <t>科技管理、人力、院所领导</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>科技管理、人力、院所领导</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
           <t>高</t>
         </is>
       </c>
+      <c r="Q69" s="2" t="inlineStr"/>
       <c r="R69" s="2" t="inlineStr"/>
       <c r="S69" s="2" t="inlineStr"/>
-      <c r="T69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr">
+        <is>
+          <t>替代人均科研产出；质量与任务贡献同行评议，不把论文/专利简单相加</t>
+        </is>
+      </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>替代人均科研产出；质量与任务贡献同行评议，不把论文/专利简单相加</t>
+          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>按项目知悉范围/部门授权；汇总、下钻、导出均需审查</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -8250,83 +7892,78 @@
       <c r="E70" s="2" t="inlineStr"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应认证且按期通过岗位能力考核人数÷本期应认证人数×100%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>本期应认证且按期通过岗位能力考核人数÷本期应认证人数×100%</t>
+          <t>人员×岗位认证周期；到期归期</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>人员×岗位认证周期；到期归期</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>HR/培训：岗位要求、应认证日、考核结果</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>HR/培训：岗位要求、应认证日、考核结果</t>
+          <t>人力资源部门</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>人力资源部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>人力、质量</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>人力、质量</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q70" s="2" t="inlineStr"/>
       <c r="R70" s="2" t="inlineStr"/>
       <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>替代难归因的培训投入产出比；只计签到不能证明能力形成</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>替代难归因的培训投入产出比；只计签到不能证明能力形成</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X70" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -8356,83 +7993,78 @@
       <c r="E71" s="2" t="inlineStr"/>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应训且完成规定课程与考核人数÷本期应训人数×100%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>本期应训且完成规定课程与考核人数÷本期应训人数×100%</t>
+          <t>人员×培训计划周期；培训类型</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>人员×培训计划周期；培训类型</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>培训：应训名单、完成课程、考核结果</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>培训：应训名单、完成课程、考核结果</t>
+          <t>人力资源部门</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>人力资源部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>人力</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>人力</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q71" s="2" t="inlineStr"/>
       <c r="R71" s="2" t="inlineStr"/>
       <c r="S71" s="2" t="inlineStr"/>
-      <c r="T71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>分母是应训人员，非全员；不同培训类型分别计算</t>
+        </is>
+      </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>分母是应训人员，非全员；不同培训类型分别计算</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X71" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -8462,83 +8094,78 @@
       <c r="E72" s="2" t="inlineStr"/>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期应结束试用且通过转正审批人数÷本期应结束试用人数×100%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>本期应结束试用且通过转正审批人数÷本期应结束试用人数×100%</t>
+          <t>试用到期 cohort；部门、用工类型</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>试用到期 cohort；部门、用工类型</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>HR：入职日、约定试用到期日、转正审批</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>HR：入职日、约定试用到期日、转正审批</t>
+          <t>人力资源部门</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>人力资源部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>人力</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>人力</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q72" s="2" t="inlineStr"/>
       <c r="R72" s="2" t="inlineStr"/>
       <c r="S72" s="2" t="inlineStr"/>
-      <c r="T72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>试用内离职需纳入原到期队列；延期单列避免幸存者偏差</t>
+        </is>
+      </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>试用内离职需纳入原到期队列；延期单列避免幸存者偏差</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X72" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -8573,78 +8200,73 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>本期有效考核中评为优秀人数÷本期有效考核人数×100%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>本期有效考核中评为优秀人数÷本期有效考核人数×100%</t>
+          <t>考核周期；同评价方案</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>考核周期；同评价方案</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>HR：有效考核对象、考核等级、方案版本</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>HR：有效考核对象、考核等级、方案版本</t>
+          <t>人力资源部门</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>人力资源部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>人力</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>人力</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="inlineStr">
-        <is>
           <t>低</t>
         </is>
       </c>
+      <c r="Q73" s="2" t="inlineStr"/>
       <c r="R73" s="2" t="inlineStr"/>
       <c r="S73" s="2" t="inlineStr"/>
-      <c r="T73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr">
+        <is>
+          <t>受优秀名额比例影响，只作分布统计；不当作部门能力排名</t>
+        </is>
+      </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>受优秀名额比例影响，只作分布统计；不当作部门能力排名</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
-        <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X73" s="2" t="inlineStr">
         <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
@@ -8678,90 +8300,85 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>否</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>期间归属于相同成本对象的人力成本÷该范围总成本×100%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>期间归属于相同成本对象的人力成本÷该范围总成本×100%</t>
+          <t>成本对象×期间；部门、项目类型</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>成本对象×期间；部门、项目类型</t>
+          <t>月；按业务时效可日刷新</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>月；按业务时效可日刷新</t>
+          <t>财务：人工成本、总成本、归集分摊记录</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>财务：人工成本、总成本、归集分摊记录</t>
+          <t>财务部门</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>财务部门</t>
+          <t>内部</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>内部</t>
+          <t>人力、财务</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>人力、财务</t>
-        </is>
-      </c>
-      <c r="Q74" s="2" t="inlineStr">
-        <is>
           <t>中</t>
         </is>
       </c>
+      <c r="Q74" s="2" t="inlineStr"/>
       <c r="R74" s="2" t="inlineStr"/>
       <c r="S74" s="2" t="inlineStr"/>
-      <c r="T74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>避免直接人工与分摊人工重复；劳动密集程度差异不代表低效</t>
+        </is>
+      </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>避免直接人工与分摊人工重复；劳动密集程度差异不代表低效</t>
+          <t>限制个人明细与小样本反推；授权范围内汇总</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>限制个人明细与小样本反推；授权范围内汇总</t>
+          <t>待业务与数据责任人确认</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>待业务与数据责任人确认</t>
-        </is>
-      </c>
-      <c r="X74" s="2" t="inlineStr">
-        <is>
           <t>待确认：适用性、字段、口径版本、目标与授权范围</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X74"/>
+  <autoFilter ref="A1:W74"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8833,7 +8450,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -8865,7 +8482,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -8897,7 +8514,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8929,7 +8546,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -8961,7 +8578,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>二期</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -8993,7 +8610,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -9025,7 +8642,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -9089,7 +8706,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -9121,7 +8738,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -9153,7 +8770,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>二期候选</t>
+          <t>三期</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9185,7 +8802,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -9217,7 +8834,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -9249,7 +8866,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -9313,7 +8930,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -9345,7 +8962,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>一期候选</t>
+          <t>一期</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -9442,7 +9059,7 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>阻断 P1：PRJ12 正式启用前必须解决</t>
+          <t>阻断一期：PRJ12 正式启用前必须解决</t>
         </is>
       </c>
     </row>
@@ -9474,7 +9091,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>阻断 P1：全部 INV 系列</t>
+          <t>阻断一期：全部 INV 库存系列</t>
         </is>
       </c>
     </row>
@@ -9506,7 +9123,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>阻断 P1：全部 PRJ 计数与经费类</t>
+          <t>阻断一期：全部 PRJ 项目计数与经费类</t>
         </is>
       </c>
     </row>
